--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.99169883164593</v>
+        <v>6.336151060142464</v>
       </c>
       <c r="D2" t="n">
-        <v>22.69164884834026</v>
+        <v>3.687392937855293</v>
       </c>
       <c r="E2" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F2" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.83481223369753</v>
+        <v>2.248156987975848</v>
       </c>
       <c r="D3" t="n">
-        <v>5.879795529170423</v>
+        <v>0.9554667734901937</v>
       </c>
       <c r="E3" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F3" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.503745188869</v>
+        <v>2.356858593191212</v>
       </c>
       <c r="D4" t="n">
-        <v>9.365575625091367</v>
+        <v>1.521906039077347</v>
       </c>
       <c r="E4" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F4" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.1003062863458</v>
+        <v>2.128799771531192</v>
       </c>
       <c r="D5" t="n">
-        <v>10.80004969132532</v>
+        <v>1.755008074840365</v>
       </c>
       <c r="E5" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F5" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.24591181869391</v>
+        <v>6.53996067053776</v>
       </c>
       <c r="D6" t="n">
-        <v>40.15260163406353</v>
+        <v>6.524797765535324</v>
       </c>
       <c r="E6" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F6" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.80498353807601</v>
+        <v>3.380809824937351</v>
       </c>
       <c r="D7" t="n">
-        <v>20.62835775241761</v>
+        <v>3.352108134767862</v>
       </c>
       <c r="E7" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F7" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.6837291567991</v>
+        <v>4.173605987979853</v>
       </c>
       <c r="D8" t="n">
-        <v>25.95488682108144</v>
+        <v>4.217669108425735</v>
       </c>
       <c r="E8" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F8" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.97214628590378</v>
+        <v>6.820473771459365</v>
       </c>
       <c r="D9" t="n">
-        <v>42.19509728966533</v>
+        <v>6.856703309570617</v>
       </c>
       <c r="E9" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F9" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.99499834362013</v>
+        <v>8.449187230838271</v>
       </c>
       <c r="D10" t="n">
-        <v>52.24221084219224</v>
+        <v>8.48935926185624</v>
       </c>
       <c r="E10" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F10" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>10.53719971234187</v>
+        <v>1.712294953255554</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>1.1375</v>
       </c>
       <c r="E11" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F11" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.4931034797685</v>
+        <v>3.817629315462382</v>
       </c>
       <c r="D12" t="n">
-        <v>14.8518536990855</v>
+        <v>2.413426226101394</v>
       </c>
       <c r="E12" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F12" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.74095494919612</v>
+        <v>6.62040517924437</v>
       </c>
       <c r="D13" t="n">
-        <v>41.65612688915245</v>
+        <v>6.769120619487274</v>
       </c>
       <c r="E13" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F13" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>25.72578300287692</v>
+        <v>4.180439737967499</v>
       </c>
       <c r="D14" t="n">
-        <v>23.90083680543424</v>
+        <v>3.883885980883064</v>
       </c>
       <c r="E14" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F14" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>48.89994822704413</v>
+        <v>7.946241586894671</v>
       </c>
       <c r="D15" t="n">
-        <v>50.60460204227093</v>
+        <v>8.223247831869026</v>
       </c>
       <c r="E15" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F15" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>48.24179737079668</v>
+        <v>7.839292072754461</v>
       </c>
       <c r="D16" t="n">
-        <v>48.47079181289532</v>
+        <v>7.87650366959549</v>
       </c>
       <c r="E16" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F16" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>16.7784267503268</v>
+        <v>2.726494346928106</v>
       </c>
       <c r="D17" t="n">
-        <v>17.74869112656328</v>
+        <v>2.884162308066533</v>
       </c>
       <c r="E17" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F17" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>7.223492080633762</v>
+        <v>1.173817463102986</v>
       </c>
       <c r="D18" t="n">
-        <v>7.054245310682931</v>
+        <v>1.146314862985976</v>
       </c>
       <c r="E18" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F18" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>22.30482153398631</v>
+        <v>3.624533499272776</v>
       </c>
       <c r="D19" t="n">
-        <v>22.84081371684468</v>
+        <v>3.711632228987261</v>
       </c>
       <c r="E19" t="n">
-        <v>14.20672279285345</v>
+        <v>2.308592453838686</v>
       </c>
       <c r="F19" t="n">
-        <v>15.60779178551577</v>
+        <v>2.536266165146313</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
